--- a/artfynd/A 47122-2024 artfynd.xlsx
+++ b/artfynd/A 47122-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121192204</v>
+        <v>121192017</v>
       </c>
       <c r="B2" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493338</v>
+        <v>493270</v>
       </c>
       <c r="R2" t="n">
-        <v>6943954</v>
+        <v>6943889</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121192421</v>
+        <v>121192594</v>
       </c>
       <c r="B3" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Tavelberget, Tavelberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493318</v>
+        <v>493413</v>
       </c>
       <c r="R3" t="n">
-        <v>6943866</v>
+        <v>6943871</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121191415</v>
+        <v>121192204</v>
       </c>
       <c r="B4" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,14 +935,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493234</v>
+        <v>493338</v>
       </c>
       <c r="R4" t="n">
-        <v>6943962</v>
+        <v>6943954</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121191337</v>
+        <v>121192421</v>
       </c>
       <c r="B5" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,14 +1047,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493270</v>
+        <v>493318</v>
       </c>
       <c r="R5" t="n">
-        <v>6943889</v>
+        <v>6943866</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,22 +1111,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121192066</v>
+        <v>121192416</v>
       </c>
       <c r="B6" t="n">
-        <v>57364</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,39 +1139,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493313</v>
+        <v>493333</v>
       </c>
       <c r="R6" t="n">
-        <v>6944004</v>
+        <v>6943877</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121191585</v>
+        <v>121191333</v>
       </c>
       <c r="B7" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,14 +1271,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493220</v>
+        <v>493280</v>
       </c>
       <c r="R7" t="n">
-        <v>6943974</v>
+        <v>6943908</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,22 +1335,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121193685</v>
+        <v>121192205</v>
       </c>
       <c r="B8" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,14 +1383,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493313</v>
+        <v>493352</v>
       </c>
       <c r="R8" t="n">
-        <v>6943851</v>
+        <v>6943961</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,22 +1447,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121193050</v>
+        <v>121191938</v>
       </c>
       <c r="B9" t="n">
-        <v>57364</v>
+        <v>78601</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,39 +1475,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tavelberget, Tavelberget, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493426</v>
+        <v>493264</v>
       </c>
       <c r="R9" t="n">
-        <v>6943860</v>
+        <v>6943993</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121191329</v>
+        <v>121192502</v>
       </c>
       <c r="B10" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1621,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493281</v>
+        <v>493396</v>
       </c>
       <c r="R10" t="n">
-        <v>6943885</v>
+        <v>6943871</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121192891</v>
+        <v>121191415</v>
       </c>
       <c r="B11" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,14 +1719,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493396</v>
+        <v>493234</v>
       </c>
       <c r="R11" t="n">
-        <v>6943825</v>
+        <v>6943962</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1768,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1793,22 +1783,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121192594</v>
+        <v>121193050</v>
       </c>
       <c r="B12" t="n">
-        <v>79679</v>
+        <v>57367</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,34 +1811,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tavelberget, Tavelberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493413</v>
+        <v>493426</v>
       </c>
       <c r="R12" t="n">
-        <v>6943871</v>
+        <v>6943860</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1880,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121192105</v>
+        <v>121191641</v>
       </c>
       <c r="B13" t="n">
-        <v>79679</v>
+        <v>78602</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1933,21 +1928,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>230405</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1957,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493326</v>
+        <v>493268</v>
       </c>
       <c r="R13" t="n">
-        <v>6944005</v>
+        <v>6944010</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1992,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121192356</v>
+        <v>121193372</v>
       </c>
       <c r="B14" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,14 +2060,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493323</v>
+        <v>493418</v>
       </c>
       <c r="R14" t="n">
-        <v>6943923</v>
+        <v>6943831</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2104,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2129,22 +2124,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121192174</v>
+        <v>121192066</v>
       </c>
       <c r="B15" t="n">
-        <v>78598</v>
+        <v>57367</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2157,34 +2152,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493346</v>
+        <v>493313</v>
       </c>
       <c r="R15" t="n">
-        <v>6943977</v>
+        <v>6944004</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2241,22 +2241,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121191333</v>
+        <v>121192106</v>
       </c>
       <c r="B16" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2269,21 +2269,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493280</v>
+        <v>493336</v>
       </c>
       <c r="R16" t="n">
-        <v>6943908</v>
+        <v>6944002</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,10 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121192205</v>
+        <v>121192891</v>
       </c>
       <c r="B17" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2401,14 +2401,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493352</v>
+        <v>493396</v>
       </c>
       <c r="R17" t="n">
-        <v>6943961</v>
+        <v>6943825</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2465,22 +2465,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121192416</v>
+        <v>121193685</v>
       </c>
       <c r="B18" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493333</v>
+        <v>493313</v>
       </c>
       <c r="R18" t="n">
-        <v>6943877</v>
+        <v>6943851</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,10 +2589,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121193372</v>
+        <v>121192356</v>
       </c>
       <c r="B19" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2625,14 +2625,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493418</v>
+        <v>493323</v>
       </c>
       <c r="R19" t="n">
-        <v>6943831</v>
+        <v>6943923</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2689,22 +2689,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121192106</v>
+        <v>121191585</v>
       </c>
       <c r="B20" t="n">
-        <v>79679</v>
+        <v>78601</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2717,34 +2717,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493336</v>
+        <v>493220</v>
       </c>
       <c r="R20" t="n">
-        <v>6944002</v>
+        <v>6943974</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2801,22 +2801,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121191641</v>
+        <v>121192174</v>
       </c>
       <c r="B21" t="n">
-        <v>78599</v>
+        <v>78601</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2829,16 +2829,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2849,14 +2849,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493268</v>
+        <v>493346</v>
       </c>
       <c r="R21" t="n">
-        <v>6944010</v>
+        <v>6943977</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2913,22 +2913,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121191938</v>
+        <v>121192105</v>
       </c>
       <c r="B22" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2941,34 +2941,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493264</v>
+        <v>493326</v>
       </c>
       <c r="R22" t="n">
-        <v>6943993</v>
+        <v>6944005</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3025,22 +3025,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121192502</v>
+        <v>121191329</v>
       </c>
       <c r="B23" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493396</v>
+        <v>493281</v>
       </c>
       <c r="R23" t="n">
-        <v>6943871</v>
+        <v>6943885</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 47122-2024 artfynd.xlsx
+++ b/artfynd/A 47122-2024 artfynd.xlsx
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121193050</v>
+        <v>121191641</v>
       </c>
       <c r="B12" t="n">
-        <v>57367</v>
+        <v>78602</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,39 +1811,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>230405</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tavelberget, Tavelberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493426</v>
+        <v>493268</v>
       </c>
       <c r="R12" t="n">
-        <v>6943860</v>
+        <v>6944010</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1900,22 +1895,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121191641</v>
+        <v>121193050</v>
       </c>
       <c r="B13" t="n">
-        <v>78602</v>
+        <v>57367</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,34 +1923,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>230405</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Tavelberget, Tavelberget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493268</v>
+        <v>493426</v>
       </c>
       <c r="R13" t="n">
-        <v>6944010</v>
+        <v>6943860</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,12 +2012,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 47122-2024 artfynd.xlsx
+++ b/artfynd/A 47122-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121192017</v>
+        <v>121191641</v>
       </c>
       <c r="B2" t="n">
-        <v>78601</v>
+        <v>78602</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493270</v>
+        <v>493268</v>
       </c>
       <c r="R2" t="n">
-        <v>6943889</v>
+        <v>6944010</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121192594</v>
+        <v>121191333</v>
       </c>
       <c r="B3" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tavelberget, Tavelberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493413</v>
+        <v>493280</v>
       </c>
       <c r="R3" t="n">
-        <v>6943871</v>
+        <v>6943908</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121192204</v>
+        <v>121192416</v>
       </c>
       <c r="B4" t="n">
         <v>78601</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493338</v>
+        <v>493333</v>
       </c>
       <c r="R4" t="n">
-        <v>6943954</v>
+        <v>6943877</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121192421</v>
+        <v>121192106</v>
       </c>
       <c r="B5" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493318</v>
+        <v>493336</v>
       </c>
       <c r="R5" t="n">
-        <v>6943866</v>
+        <v>6944002</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121192416</v>
+        <v>121192594</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,34 +1139,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Tavelberget, Tavelberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493333</v>
+        <v>493413</v>
       </c>
       <c r="R6" t="n">
-        <v>6943877</v>
+        <v>6943871</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,19 +1223,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121191333</v>
+        <v>121192421</v>
       </c>
       <c r="B7" t="n">
         <v>78601</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493280</v>
+        <v>493318</v>
       </c>
       <c r="R7" t="n">
-        <v>6943908</v>
+        <v>6943866</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121192205</v>
+        <v>121192204</v>
       </c>
       <c r="B8" t="n">
         <v>78601</v>
@@ -1383,14 +1383,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493352</v>
+        <v>493338</v>
       </c>
       <c r="R8" t="n">
-        <v>6943961</v>
+        <v>6943954</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,22 +1447,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121191938</v>
+        <v>121193050</v>
       </c>
       <c r="B9" t="n">
-        <v>78601</v>
+        <v>57367</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,34 +1475,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Tavelberget, Tavelberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493264</v>
+        <v>493426</v>
       </c>
       <c r="R9" t="n">
-        <v>6943993</v>
+        <v>6943860</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,7 +1576,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121192502</v>
+        <v>121192356</v>
       </c>
       <c r="B10" t="n">
         <v>78601</v>
@@ -1611,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493396</v>
+        <v>493323</v>
       </c>
       <c r="R10" t="n">
-        <v>6943871</v>
+        <v>6943923</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,7 +1688,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121191415</v>
+        <v>121192205</v>
       </c>
       <c r="B11" t="n">
         <v>78601</v>
@@ -1719,14 +1724,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493234</v>
+        <v>493352</v>
       </c>
       <c r="R11" t="n">
-        <v>6943962</v>
+        <v>6943961</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121191641</v>
+        <v>121191367</v>
       </c>
       <c r="B12" t="n">
-        <v>78602</v>
+        <v>78601</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,16 +1816,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1835,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493268</v>
+        <v>493270</v>
       </c>
       <c r="R12" t="n">
-        <v>6944010</v>
+        <v>6943889</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121193050</v>
+        <v>121193372</v>
       </c>
       <c r="B13" t="n">
-        <v>57367</v>
+        <v>78601</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,39 +1928,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tavelberget, Tavelberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493426</v>
+        <v>493418</v>
       </c>
       <c r="R13" t="n">
-        <v>6943860</v>
+        <v>6943831</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,19 +2012,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121193372</v>
+        <v>121192502</v>
       </c>
       <c r="B14" t="n">
         <v>78601</v>
@@ -2060,14 +2060,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493418</v>
+        <v>493396</v>
       </c>
       <c r="R14" t="n">
-        <v>6943831</v>
+        <v>6943871</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2124,22 +2124,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121192066</v>
+        <v>121192105</v>
       </c>
       <c r="B15" t="n">
-        <v>57367</v>
+        <v>79682</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,39 +2152,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493313</v>
+        <v>493326</v>
       </c>
       <c r="R15" t="n">
-        <v>6944004</v>
+        <v>6944005</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2216,7 +2211,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2226,7 +2221,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121192106</v>
+        <v>121192066</v>
       </c>
       <c r="B16" t="n">
-        <v>79682</v>
+        <v>57367</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2269,34 +2264,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493336</v>
+        <v>493313</v>
       </c>
       <c r="R16" t="n">
-        <v>6944002</v>
+        <v>6944004</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2353,19 +2353,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121192891</v>
+        <v>121191585</v>
       </c>
       <c r="B17" t="n">
         <v>78601</v>
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493396</v>
+        <v>493220</v>
       </c>
       <c r="R17" t="n">
-        <v>6943825</v>
+        <v>6943974</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2477,7 +2477,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121193685</v>
+        <v>121191329</v>
       </c>
       <c r="B18" t="n">
         <v>78601</v>
@@ -2513,14 +2513,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493313</v>
+        <v>493281</v>
       </c>
       <c r="R18" t="n">
-        <v>6943851</v>
+        <v>6943885</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2577,19 +2577,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121192356</v>
+        <v>121193685</v>
       </c>
       <c r="B19" t="n">
         <v>78601</v>
@@ -2625,14 +2625,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493323</v>
+        <v>493313</v>
       </c>
       <c r="R19" t="n">
-        <v>6943923</v>
+        <v>6943851</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2689,19 +2689,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121191585</v>
+        <v>121192891</v>
       </c>
       <c r="B20" t="n">
         <v>78601</v>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493220</v>
+        <v>493396</v>
       </c>
       <c r="R20" t="n">
-        <v>6943974</v>
+        <v>6943825</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,7 +2813,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121192174</v>
+        <v>121191415</v>
       </c>
       <c r="B21" t="n">
         <v>78601</v>
@@ -2849,14 +2849,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493346</v>
+        <v>493234</v>
       </c>
       <c r="R21" t="n">
-        <v>6943977</v>
+        <v>6943962</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2925,10 +2925,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121192105</v>
+        <v>121192174</v>
       </c>
       <c r="B22" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2941,34 +2941,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493326</v>
+        <v>493346</v>
       </c>
       <c r="R22" t="n">
-        <v>6944005</v>
+        <v>6943977</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3025,19 +3025,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121191329</v>
+        <v>121191938</v>
       </c>
       <c r="B23" t="n">
         <v>78601</v>
@@ -3073,14 +3073,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493281</v>
+        <v>493264</v>
       </c>
       <c r="R23" t="n">
-        <v>6943885</v>
+        <v>6943993</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 47122-2024 artfynd.xlsx
+++ b/artfynd/A 47122-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121191641</v>
+        <v>121192421</v>
       </c>
       <c r="B2" t="n">
-        <v>78602</v>
+        <v>78604</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493268</v>
+        <v>493318</v>
       </c>
       <c r="R2" t="n">
-        <v>6944010</v>
+        <v>6943866</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121191333</v>
+        <v>121192891</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,14 +823,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493280</v>
+        <v>493396</v>
       </c>
       <c r="R3" t="n">
-        <v>6943908</v>
+        <v>6943825</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121192416</v>
+        <v>121192594</v>
       </c>
       <c r="B4" t="n">
-        <v>78601</v>
+        <v>79685</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Tavelberget, Tavelberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493333</v>
+        <v>493413</v>
       </c>
       <c r="R4" t="n">
-        <v>6943877</v>
+        <v>6943871</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121192106</v>
+        <v>121191585</v>
       </c>
       <c r="B5" t="n">
-        <v>79682</v>
+        <v>78604</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493336</v>
+        <v>493220</v>
       </c>
       <c r="R5" t="n">
-        <v>6944002</v>
+        <v>6943974</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,22 +1111,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121192594</v>
+        <v>121192416</v>
       </c>
       <c r="B6" t="n">
-        <v>79682</v>
+        <v>78604</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,34 +1139,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tavelberget, Tavelberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493413</v>
+        <v>493333</v>
       </c>
       <c r="R6" t="n">
-        <v>6943871</v>
+        <v>6943877</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,22 +1223,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121192421</v>
+        <v>121192205</v>
       </c>
       <c r="B7" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493318</v>
+        <v>493352</v>
       </c>
       <c r="R7" t="n">
-        <v>6943866</v>
+        <v>6943961</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121192204</v>
+        <v>121191938</v>
       </c>
       <c r="B8" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,14 +1383,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493338</v>
+        <v>493264</v>
       </c>
       <c r="R8" t="n">
-        <v>6943954</v>
+        <v>6943993</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,22 +1447,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121193050</v>
+        <v>121191415</v>
       </c>
       <c r="B9" t="n">
-        <v>57367</v>
+        <v>78604</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,39 +1475,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tavelberget, Tavelberget, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493426</v>
+        <v>493234</v>
       </c>
       <c r="R9" t="n">
-        <v>6943860</v>
+        <v>6943962</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121192356</v>
+        <v>121191333</v>
       </c>
       <c r="B10" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493323</v>
+        <v>493280</v>
       </c>
       <c r="R10" t="n">
-        <v>6943923</v>
+        <v>6943908</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121192205</v>
+        <v>121191329</v>
       </c>
       <c r="B11" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493352</v>
+        <v>493281</v>
       </c>
       <c r="R11" t="n">
-        <v>6943961</v>
+        <v>6943885</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121191367</v>
+        <v>121192204</v>
       </c>
       <c r="B12" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493270</v>
+        <v>493338</v>
       </c>
       <c r="R12" t="n">
-        <v>6943889</v>
+        <v>6943954</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121193372</v>
+        <v>121192174</v>
       </c>
       <c r="B13" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1948,14 +1943,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493418</v>
+        <v>493346</v>
       </c>
       <c r="R13" t="n">
-        <v>6943831</v>
+        <v>6943977</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,12 +2007,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2027,7 +2022,7 @@
         <v>121192502</v>
       </c>
       <c r="B14" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2136,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121192105</v>
+        <v>121192356</v>
       </c>
       <c r="B15" t="n">
-        <v>79682</v>
+        <v>78604</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,34 +2147,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493326</v>
+        <v>493323</v>
       </c>
       <c r="R15" t="n">
-        <v>6944005</v>
+        <v>6943923</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2211,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2236,22 +2231,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121192066</v>
+        <v>121191367</v>
       </c>
       <c r="B16" t="n">
-        <v>57367</v>
+        <v>78604</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,39 +2259,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493313</v>
+        <v>493270</v>
       </c>
       <c r="R16" t="n">
-        <v>6944004</v>
+        <v>6943889</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2328,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2338,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121191585</v>
+        <v>121193372</v>
       </c>
       <c r="B17" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2405,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493220</v>
+        <v>493418</v>
       </c>
       <c r="R17" t="n">
-        <v>6943974</v>
+        <v>6943831</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2440,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2477,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121191329</v>
+        <v>121193050</v>
       </c>
       <c r="B18" t="n">
-        <v>78601</v>
+        <v>57367</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2493,34 +2483,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Tavelberget, Tavelberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493281</v>
+        <v>493426</v>
       </c>
       <c r="R18" t="n">
-        <v>6943885</v>
+        <v>6943860</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2552,7 +2547,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2562,7 +2557,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121193685</v>
+        <v>121192105</v>
       </c>
       <c r="B19" t="n">
-        <v>78601</v>
+        <v>79685</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2605,21 +2600,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2629,10 +2624,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493313</v>
+        <v>493326</v>
       </c>
       <c r="R19" t="n">
-        <v>6943851</v>
+        <v>6944005</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2664,7 +2659,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2674,7 +2669,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2701,10 +2696,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121192891</v>
+        <v>121192106</v>
       </c>
       <c r="B20" t="n">
-        <v>78601</v>
+        <v>79685</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2717,34 +2712,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493396</v>
+        <v>493336</v>
       </c>
       <c r="R20" t="n">
-        <v>6943825</v>
+        <v>6944002</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2776,7 +2771,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,7 +2781,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2801,22 +2796,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121191415</v>
+        <v>121191641</v>
       </c>
       <c r="B21" t="n">
-        <v>78601</v>
+        <v>78605</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2829,16 +2824,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2849,14 +2844,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493234</v>
+        <v>493268</v>
       </c>
       <c r="R21" t="n">
-        <v>6943962</v>
+        <v>6944010</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2888,7 +2883,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2898,7 +2893,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2913,22 +2908,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121192174</v>
+        <v>121192066</v>
       </c>
       <c r="B22" t="n">
-        <v>78601</v>
+        <v>57367</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2941,34 +2936,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493346</v>
+        <v>493313</v>
       </c>
       <c r="R22" t="n">
-        <v>6943977</v>
+        <v>6944004</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3025,22 +3025,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121191938</v>
+        <v>121193685</v>
       </c>
       <c r="B23" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3073,14 +3073,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493264</v>
+        <v>493313</v>
       </c>
       <c r="R23" t="n">
-        <v>6943993</v>
+        <v>6943851</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3137,12 +3137,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 47122-2024 artfynd.xlsx
+++ b/artfynd/A 47122-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121192421</v>
+        <v>121191333</v>
       </c>
       <c r="B2" t="n">
         <v>78604</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493318</v>
+        <v>493280</v>
       </c>
       <c r="R2" t="n">
-        <v>6943866</v>
+        <v>6943908</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121192891</v>
+        <v>121192204</v>
       </c>
       <c r="B3" t="n">
         <v>78604</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493396</v>
+        <v>493338</v>
       </c>
       <c r="R3" t="n">
-        <v>6943825</v>
+        <v>6943954</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121192594</v>
+        <v>121193050</v>
       </c>
       <c r="B4" t="n">
-        <v>79685</v>
+        <v>57367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tavelberget, Tavelberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493413</v>
+        <v>493426</v>
       </c>
       <c r="R4" t="n">
-        <v>6943871</v>
+        <v>6943860</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121191585</v>
+        <v>121192502</v>
       </c>
       <c r="B5" t="n">
         <v>78604</v>
@@ -1047,14 +1052,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493220</v>
+        <v>493396</v>
       </c>
       <c r="R5" t="n">
-        <v>6943974</v>
+        <v>6943871</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,19 +1116,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121192416</v>
+        <v>121191329</v>
       </c>
       <c r="B6" t="n">
         <v>78604</v>
@@ -1159,14 +1164,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493333</v>
+        <v>493281</v>
       </c>
       <c r="R6" t="n">
-        <v>6943877</v>
+        <v>6943885</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,19 +1228,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121192205</v>
+        <v>121191367</v>
       </c>
       <c r="B7" t="n">
         <v>78604</v>
@@ -1271,14 +1276,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493352</v>
+        <v>493270</v>
       </c>
       <c r="R7" t="n">
-        <v>6943961</v>
+        <v>6943889</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,19 +1340,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121191938</v>
+        <v>121193372</v>
       </c>
       <c r="B8" t="n">
         <v>78604</v>
@@ -1383,14 +1388,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493264</v>
+        <v>493418</v>
       </c>
       <c r="R8" t="n">
-        <v>6943993</v>
+        <v>6943831</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,12 +1452,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1571,7 +1576,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121191333</v>
+        <v>121191585</v>
       </c>
       <c r="B10" t="n">
         <v>78604</v>
@@ -1607,14 +1612,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493280</v>
+        <v>493220</v>
       </c>
       <c r="R10" t="n">
-        <v>6943908</v>
+        <v>6943974</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,19 +1676,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121191329</v>
+        <v>121192416</v>
       </c>
       <c r="B11" t="n">
         <v>78604</v>
@@ -1719,14 +1724,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493281</v>
+        <v>493333</v>
       </c>
       <c r="R11" t="n">
-        <v>6943885</v>
+        <v>6943877</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,19 +1788,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121192204</v>
+        <v>121193685</v>
       </c>
       <c r="B12" t="n">
         <v>78604</v>
@@ -1835,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493338</v>
+        <v>493313</v>
       </c>
       <c r="R12" t="n">
-        <v>6943954</v>
+        <v>6943851</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121192174</v>
+        <v>121192106</v>
       </c>
       <c r="B13" t="n">
-        <v>78604</v>
+        <v>79685</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,21 +1928,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493346</v>
+        <v>493336</v>
       </c>
       <c r="R13" t="n">
-        <v>6943977</v>
+        <v>6944002</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1982,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,7 +2024,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121192502</v>
+        <v>121192891</v>
       </c>
       <c r="B14" t="n">
         <v>78604</v>
@@ -2055,14 +2060,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
         <v>493396</v>
       </c>
       <c r="R14" t="n">
-        <v>6943871</v>
+        <v>6943825</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2094,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2119,19 +2124,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121192356</v>
+        <v>121192174</v>
       </c>
       <c r="B15" t="n">
         <v>78604</v>
@@ -2171,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493323</v>
+        <v>493346</v>
       </c>
       <c r="R15" t="n">
-        <v>6943923</v>
+        <v>6943977</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2206,7 +2211,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2221,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121191367</v>
+        <v>121192066</v>
       </c>
       <c r="B16" t="n">
-        <v>78604</v>
+        <v>57367</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,34 +2264,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493270</v>
+        <v>493313</v>
       </c>
       <c r="R16" t="n">
-        <v>6943889</v>
+        <v>6944004</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2318,7 +2328,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2338,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121193372</v>
+        <v>121191641</v>
       </c>
       <c r="B17" t="n">
-        <v>78604</v>
+        <v>78605</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,16 +2381,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2395,10 +2405,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493418</v>
+        <v>493268</v>
       </c>
       <c r="R17" t="n">
-        <v>6943831</v>
+        <v>6944010</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2430,7 +2440,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2450,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,10 +2477,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121193050</v>
+        <v>121191938</v>
       </c>
       <c r="B18" t="n">
-        <v>57367</v>
+        <v>78604</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2483,39 +2493,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tavelberget, Tavelberget, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493426</v>
+        <v>493264</v>
       </c>
       <c r="R18" t="n">
-        <v>6943860</v>
+        <v>6943993</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2547,7 +2552,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2557,7 +2562,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2584,10 +2589,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121192105</v>
+        <v>121192421</v>
       </c>
       <c r="B19" t="n">
-        <v>79685</v>
+        <v>78604</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2600,34 +2605,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493326</v>
+        <v>493318</v>
       </c>
       <c r="R19" t="n">
-        <v>6944005</v>
+        <v>6943866</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2659,7 +2664,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2669,7 +2674,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2684,22 +2689,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121192106</v>
+        <v>121192356</v>
       </c>
       <c r="B20" t="n">
-        <v>79685</v>
+        <v>78604</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2712,21 +2717,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2736,10 +2741,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493336</v>
+        <v>493323</v>
       </c>
       <c r="R20" t="n">
-        <v>6944002</v>
+        <v>6943923</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2771,7 +2776,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2781,7 +2786,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2808,10 +2813,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121191641</v>
+        <v>121192594</v>
       </c>
       <c r="B21" t="n">
-        <v>78605</v>
+        <v>79685</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2824,34 +2829,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Tavelberget, Tavelberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493268</v>
+        <v>493413</v>
       </c>
       <c r="R21" t="n">
-        <v>6944010</v>
+        <v>6943871</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2883,7 +2888,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2893,7 +2898,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2908,22 +2913,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121192066</v>
+        <v>121192205</v>
       </c>
       <c r="B22" t="n">
-        <v>57367</v>
+        <v>78604</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2936,39 +2941,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493313</v>
+        <v>493352</v>
       </c>
       <c r="R22" t="n">
-        <v>6944004</v>
+        <v>6943961</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3025,22 +3025,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121193685</v>
+        <v>121192105</v>
       </c>
       <c r="B23" t="n">
-        <v>78604</v>
+        <v>79685</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3053,21 +3053,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493313</v>
+        <v>493326</v>
       </c>
       <c r="R23" t="n">
-        <v>6943851</v>
+        <v>6944005</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 47122-2024 artfynd.xlsx
+++ b/artfynd/A 47122-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121191333</v>
+        <v>121193050</v>
       </c>
       <c r="B2" t="n">
-        <v>78604</v>
+        <v>57370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Tavelberget, Tavelberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493280</v>
+        <v>493426</v>
       </c>
       <c r="R2" t="n">
-        <v>6943908</v>
+        <v>6943860</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121192204</v>
+        <v>121192066</v>
       </c>
       <c r="B3" t="n">
-        <v>78604</v>
+        <v>57370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +808,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493338</v>
+        <v>493313</v>
       </c>
       <c r="R3" t="n">
-        <v>6943954</v>
+        <v>6944004</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121193050</v>
+        <v>121192356</v>
       </c>
       <c r="B4" t="n">
-        <v>57367</v>
+        <v>78607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tavelberget, Tavelberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493426</v>
+        <v>493323</v>
       </c>
       <c r="R4" t="n">
-        <v>6943860</v>
+        <v>6943923</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121192502</v>
+        <v>121192205</v>
       </c>
       <c r="B5" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493396</v>
+        <v>493352</v>
       </c>
       <c r="R5" t="n">
-        <v>6943871</v>
+        <v>6943961</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121191329</v>
+        <v>121193685</v>
       </c>
       <c r="B6" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,14 +1169,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493281</v>
+        <v>493313</v>
       </c>
       <c r="R6" t="n">
-        <v>6943885</v>
+        <v>6943851</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,22 +1233,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121191367</v>
+        <v>121193372</v>
       </c>
       <c r="B7" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493270</v>
+        <v>493418</v>
       </c>
       <c r="R7" t="n">
-        <v>6943889</v>
+        <v>6943831</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121193372</v>
+        <v>121192502</v>
       </c>
       <c r="B8" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,14 +1393,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493418</v>
+        <v>493396</v>
       </c>
       <c r="R8" t="n">
-        <v>6943831</v>
+        <v>6943871</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,22 +1457,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121191415</v>
+        <v>121191337</v>
       </c>
       <c r="B9" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,14 +1505,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493234</v>
+        <v>493270</v>
       </c>
       <c r="R9" t="n">
-        <v>6943962</v>
+        <v>6943889</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1564,22 +1569,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121191585</v>
+        <v>121192106</v>
       </c>
       <c r="B10" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,34 +1597,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493220</v>
+        <v>493336</v>
       </c>
       <c r="R10" t="n">
-        <v>6943974</v>
+        <v>6944002</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,22 +1681,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121192416</v>
+        <v>121191329</v>
       </c>
       <c r="B11" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,14 +1729,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493333</v>
+        <v>493281</v>
       </c>
       <c r="R11" t="n">
-        <v>6943877</v>
+        <v>6943885</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1788,22 +1793,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121193685</v>
+        <v>121192105</v>
       </c>
       <c r="B12" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,21 +1821,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493313</v>
+        <v>493326</v>
       </c>
       <c r="R12" t="n">
-        <v>6943851</v>
+        <v>6944005</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121192106</v>
+        <v>121191938</v>
       </c>
       <c r="B13" t="n">
-        <v>79685</v>
+        <v>78607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,34 +1933,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493336</v>
+        <v>493264</v>
       </c>
       <c r="R13" t="n">
-        <v>6944002</v>
+        <v>6943993</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +2002,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,10 +2029,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121192891</v>
+        <v>121191641</v>
       </c>
       <c r="B14" t="n">
-        <v>78604</v>
+        <v>78608</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,16 +2045,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2064,10 +2069,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493396</v>
+        <v>493268</v>
       </c>
       <c r="R14" t="n">
-        <v>6943825</v>
+        <v>6944010</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2099,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,10 +2141,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121192174</v>
+        <v>121191585</v>
       </c>
       <c r="B15" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2172,14 +2177,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493346</v>
+        <v>493220</v>
       </c>
       <c r="R15" t="n">
-        <v>6943977</v>
+        <v>6943974</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2211,7 +2216,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,7 +2226,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2236,22 +2241,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121192066</v>
+        <v>121191415</v>
       </c>
       <c r="B16" t="n">
-        <v>57367</v>
+        <v>78607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,39 +2269,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493313</v>
+        <v>493234</v>
       </c>
       <c r="R16" t="n">
-        <v>6944004</v>
+        <v>6943962</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2353,22 +2353,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121191641</v>
+        <v>121192891</v>
       </c>
       <c r="B17" t="n">
-        <v>78605</v>
+        <v>78607</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493268</v>
+        <v>493396</v>
       </c>
       <c r="R17" t="n">
-        <v>6944010</v>
+        <v>6943825</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2477,10 +2477,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121191938</v>
+        <v>121192594</v>
       </c>
       <c r="B18" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2493,34 +2493,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Tavelberget, Tavelberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493264</v>
+        <v>493413</v>
       </c>
       <c r="R18" t="n">
-        <v>6943993</v>
+        <v>6943871</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,10 +2589,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121192421</v>
+        <v>121192174</v>
       </c>
       <c r="B19" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493318</v>
+        <v>493346</v>
       </c>
       <c r="R19" t="n">
-        <v>6943866</v>
+        <v>6943977</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2701,10 +2701,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121192356</v>
+        <v>121192204</v>
       </c>
       <c r="B20" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2737,14 +2737,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493323</v>
+        <v>493338</v>
       </c>
       <c r="R20" t="n">
-        <v>6943923</v>
+        <v>6943954</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2801,22 +2801,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121192594</v>
+        <v>121192421</v>
       </c>
       <c r="B21" t="n">
-        <v>79685</v>
+        <v>78607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2829,34 +2829,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Tavelberget, Tavelberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493413</v>
+        <v>493318</v>
       </c>
       <c r="R21" t="n">
-        <v>6943871</v>
+        <v>6943866</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2925,10 +2925,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121192205</v>
+        <v>121192416</v>
       </c>
       <c r="B22" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2961,14 +2961,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493352</v>
+        <v>493333</v>
       </c>
       <c r="R22" t="n">
-        <v>6943961</v>
+        <v>6943877</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3025,22 +3025,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121192105</v>
+        <v>121191333</v>
       </c>
       <c r="B23" t="n">
-        <v>79685</v>
+        <v>78607</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3053,34 +3053,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493326</v>
+        <v>493280</v>
       </c>
       <c r="R23" t="n">
-        <v>6944005</v>
+        <v>6943908</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3137,12 +3137,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 47122-2024 artfynd.xlsx
+++ b/artfynd/A 47122-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121193050</v>
+        <v>121191938</v>
       </c>
       <c r="B2" t="n">
-        <v>57370</v>
+        <v>78607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tavelberget, Tavelberget, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493426</v>
+        <v>493264</v>
       </c>
       <c r="R2" t="n">
-        <v>6943860</v>
+        <v>6943993</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121192066</v>
+        <v>121192017</v>
       </c>
       <c r="B3" t="n">
-        <v>57370</v>
+        <v>78607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493313</v>
+        <v>493270</v>
       </c>
       <c r="R3" t="n">
-        <v>6944004</v>
+        <v>6943889</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121192356</v>
+        <v>121191329</v>
       </c>
       <c r="B4" t="n">
         <v>78607</v>
@@ -949,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493323</v>
+        <v>493281</v>
       </c>
       <c r="R4" t="n">
-        <v>6943923</v>
+        <v>6943885</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121192205</v>
+        <v>121191415</v>
       </c>
       <c r="B5" t="n">
         <v>78607</v>
@@ -1057,14 +1047,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493352</v>
+        <v>493234</v>
       </c>
       <c r="R5" t="n">
-        <v>6943961</v>
+        <v>6943962</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121193685</v>
+        <v>121192204</v>
       </c>
       <c r="B6" t="n">
         <v>78607</v>
@@ -1173,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493313</v>
+        <v>493338</v>
       </c>
       <c r="R6" t="n">
-        <v>6943851</v>
+        <v>6943954</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1357,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121192502</v>
+        <v>121192174</v>
       </c>
       <c r="B8" t="n">
         <v>78607</v>
@@ -1397,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493396</v>
+        <v>493346</v>
       </c>
       <c r="R8" t="n">
-        <v>6943871</v>
+        <v>6943977</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121191337</v>
+        <v>121191641</v>
       </c>
       <c r="B9" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,16 +1475,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1509,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493270</v>
+        <v>493268</v>
       </c>
       <c r="R9" t="n">
-        <v>6943889</v>
+        <v>6944010</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1693,7 +1683,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121191329</v>
+        <v>121191585</v>
       </c>
       <c r="B11" t="n">
         <v>78607</v>
@@ -1729,14 +1719,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493281</v>
+        <v>493220</v>
       </c>
       <c r="R11" t="n">
-        <v>6943885</v>
+        <v>6943974</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1768,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1793,22 +1783,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121192105</v>
+        <v>121192421</v>
       </c>
       <c r="B12" t="n">
-        <v>79688</v>
+        <v>78607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,34 +1811,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493326</v>
+        <v>493318</v>
       </c>
       <c r="R12" t="n">
-        <v>6944005</v>
+        <v>6943866</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1880,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1905,19 +1895,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121191938</v>
+        <v>121192502</v>
       </c>
       <c r="B13" t="n">
         <v>78607</v>
@@ -1953,14 +1943,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493264</v>
+        <v>493396</v>
       </c>
       <c r="R13" t="n">
-        <v>6943993</v>
+        <v>6943871</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1992,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121191641</v>
+        <v>121191333</v>
       </c>
       <c r="B14" t="n">
-        <v>78608</v>
+        <v>78607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,16 +2035,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2065,14 +2055,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493268</v>
+        <v>493280</v>
       </c>
       <c r="R14" t="n">
-        <v>6944010</v>
+        <v>6943908</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2104,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2129,22 +2119,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121191585</v>
+        <v>121192066</v>
       </c>
       <c r="B15" t="n">
-        <v>78607</v>
+        <v>57370</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2157,34 +2147,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493220</v>
+        <v>493313</v>
       </c>
       <c r="R15" t="n">
-        <v>6943974</v>
+        <v>6944004</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2216,7 +2211,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2226,7 +2221,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,7 +2248,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121191415</v>
+        <v>121192205</v>
       </c>
       <c r="B16" t="n">
         <v>78607</v>
@@ -2289,14 +2284,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493234</v>
+        <v>493352</v>
       </c>
       <c r="R16" t="n">
-        <v>6943962</v>
+        <v>6943961</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2328,7 +2323,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2338,7 +2333,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,10 +2360,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121192891</v>
+        <v>121192594</v>
       </c>
       <c r="B17" t="n">
-        <v>78607</v>
+        <v>79688</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2381,34 +2376,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Tavelberget, Tavelberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493396</v>
+        <v>493413</v>
       </c>
       <c r="R17" t="n">
-        <v>6943825</v>
+        <v>6943871</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2440,7 +2435,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,7 +2445,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2465,22 +2460,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121192594</v>
+        <v>121192416</v>
       </c>
       <c r="B18" t="n">
-        <v>79688</v>
+        <v>78607</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2493,34 +2488,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tavelberget, Tavelberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493413</v>
+        <v>493333</v>
       </c>
       <c r="R18" t="n">
-        <v>6943871</v>
+        <v>6943877</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2552,7 +2547,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2562,7 +2557,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2577,22 +2572,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121192174</v>
+        <v>121193050</v>
       </c>
       <c r="B19" t="n">
-        <v>78607</v>
+        <v>57370</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2605,34 +2600,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Tavelberget, Tavelberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493346</v>
+        <v>493426</v>
       </c>
       <c r="R19" t="n">
-        <v>6943977</v>
+        <v>6943860</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2701,7 +2701,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121192204</v>
+        <v>121192891</v>
       </c>
       <c r="B20" t="n">
         <v>78607</v>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493338</v>
+        <v>493396</v>
       </c>
       <c r="R20" t="n">
-        <v>6943954</v>
+        <v>6943825</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,7 +2813,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121192421</v>
+        <v>121192356</v>
       </c>
       <c r="B21" t="n">
         <v>78607</v>
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493318</v>
+        <v>493323</v>
       </c>
       <c r="R21" t="n">
-        <v>6943866</v>
+        <v>6943923</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2925,7 +2925,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121192416</v>
+        <v>121193685</v>
       </c>
       <c r="B22" t="n">
         <v>78607</v>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493333</v>
+        <v>493313</v>
       </c>
       <c r="R22" t="n">
-        <v>6943877</v>
+        <v>6943851</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3037,10 +3037,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121191333</v>
+        <v>121192105</v>
       </c>
       <c r="B23" t="n">
-        <v>78607</v>
+        <v>79688</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3053,34 +3053,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493280</v>
+        <v>493326</v>
       </c>
       <c r="R23" t="n">
-        <v>6943908</v>
+        <v>6944005</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3137,12 +3137,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 47122-2024 artfynd.xlsx
+++ b/artfynd/A 47122-2024 artfynd.xlsx
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121192066</v>
+        <v>121192205</v>
       </c>
       <c r="B15" t="n">
-        <v>57370</v>
+        <v>78607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,39 +2147,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493313</v>
+        <v>493352</v>
       </c>
       <c r="R15" t="n">
-        <v>6944004</v>
+        <v>6943961</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2211,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2236,22 +2231,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121192205</v>
+        <v>121192594</v>
       </c>
       <c r="B16" t="n">
-        <v>78607</v>
+        <v>79688</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,34 +2259,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Tavelberget, Tavelberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493352</v>
+        <v>493413</v>
       </c>
       <c r="R16" t="n">
-        <v>6943961</v>
+        <v>6943871</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2323,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2333,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2360,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121192594</v>
+        <v>121192416</v>
       </c>
       <c r="B17" t="n">
-        <v>79688</v>
+        <v>78607</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2376,34 +2371,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tavelberget, Tavelberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493413</v>
+        <v>493333</v>
       </c>
       <c r="R17" t="n">
-        <v>6943871</v>
+        <v>6943877</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2435,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2445,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2460,22 +2455,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121192416</v>
+        <v>121193050</v>
       </c>
       <c r="B18" t="n">
-        <v>78607</v>
+        <v>57370</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2488,34 +2483,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Tavelberget, Tavelberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493333</v>
+        <v>493426</v>
       </c>
       <c r="R18" t="n">
-        <v>6943877</v>
+        <v>6943860</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2572,22 +2572,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121193050</v>
+        <v>121192891</v>
       </c>
       <c r="B19" t="n">
-        <v>57370</v>
+        <v>78607</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2600,39 +2600,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tavelberget, Tavelberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493426</v>
+        <v>493396</v>
       </c>
       <c r="R19" t="n">
-        <v>6943860</v>
+        <v>6943825</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2664,7 +2659,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2674,7 +2669,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2689,19 +2684,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121192891</v>
+        <v>121192356</v>
       </c>
       <c r="B20" t="n">
         <v>78607</v>
@@ -2737,14 +2732,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493396</v>
+        <v>493323</v>
       </c>
       <c r="R20" t="n">
-        <v>6943825</v>
+        <v>6943923</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2776,7 +2771,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,7 +2781,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2801,19 +2796,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121192356</v>
+        <v>121193685</v>
       </c>
       <c r="B21" t="n">
         <v>78607</v>
@@ -2849,14 +2844,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493323</v>
+        <v>493313</v>
       </c>
       <c r="R21" t="n">
-        <v>6943923</v>
+        <v>6943851</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2888,7 +2883,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2898,7 +2893,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2913,22 +2908,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121193685</v>
+        <v>121192105</v>
       </c>
       <c r="B22" t="n">
-        <v>78607</v>
+        <v>79688</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2941,21 +2936,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2965,10 +2960,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493313</v>
+        <v>493326</v>
       </c>
       <c r="R22" t="n">
-        <v>6943851</v>
+        <v>6944005</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3000,7 +2995,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3010,7 +3005,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3037,14 +3032,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121192105</v>
+        <v>121192066</v>
       </c>
       <c r="B23" t="n">
-        <v>79688</v>
+        <v>57371</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3053,34 +3048,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493326</v>
+        <v>493313</v>
       </c>
       <c r="R23" t="n">
-        <v>6944005</v>
+        <v>6944004</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 47122-2024 artfynd.xlsx
+++ b/artfynd/A 47122-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121191938</v>
+        <v>121193685</v>
       </c>
       <c r="B2" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493264</v>
+        <v>493313</v>
       </c>
       <c r="R2" t="n">
-        <v>6943993</v>
+        <v>6943851</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121192017</v>
+        <v>121192502</v>
       </c>
       <c r="B3" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,14 +823,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493270</v>
+        <v>493396</v>
       </c>
       <c r="R3" t="n">
-        <v>6943889</v>
+        <v>6943871</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121191329</v>
+        <v>121193372</v>
       </c>
       <c r="B4" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,14 +935,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493281</v>
+        <v>493418</v>
       </c>
       <c r="R4" t="n">
-        <v>6943885</v>
+        <v>6943831</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121191415</v>
+        <v>121192205</v>
       </c>
       <c r="B5" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,14 +1047,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493234</v>
+        <v>493352</v>
       </c>
       <c r="R5" t="n">
-        <v>6943962</v>
+        <v>6943961</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121192204</v>
+        <v>121192891</v>
       </c>
       <c r="B6" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493338</v>
+        <v>493396</v>
       </c>
       <c r="R6" t="n">
-        <v>6943954</v>
+        <v>6943825</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121193372</v>
+        <v>121191329</v>
       </c>
       <c r="B7" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,14 +1271,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493418</v>
+        <v>493281</v>
       </c>
       <c r="R7" t="n">
-        <v>6943831</v>
+        <v>6943885</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,22 +1335,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121192174</v>
+        <v>121191415</v>
       </c>
       <c r="B8" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,14 +1383,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493346</v>
+        <v>493234</v>
       </c>
       <c r="R8" t="n">
-        <v>6943977</v>
+        <v>6943962</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121191641</v>
+        <v>121192017</v>
       </c>
       <c r="B9" t="n">
         <v>78608</v>
@@ -1475,16 +1475,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493268</v>
+        <v>493270</v>
       </c>
       <c r="R9" t="n">
-        <v>6944010</v>
+        <v>6943889</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,7 +1574,7 @@
         <v>121192106</v>
       </c>
       <c r="B10" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121191585</v>
+        <v>121191333</v>
       </c>
       <c r="B11" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,14 +1719,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493220</v>
+        <v>493280</v>
       </c>
       <c r="R11" t="n">
-        <v>6943974</v>
+        <v>6943908</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,22 +1783,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121192421</v>
+        <v>121192174</v>
       </c>
       <c r="B12" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493318</v>
+        <v>493346</v>
       </c>
       <c r="R12" t="n">
-        <v>6943866</v>
+        <v>6943977</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121192502</v>
+        <v>121192105</v>
       </c>
       <c r="B13" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,34 +1923,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493396</v>
+        <v>493326</v>
       </c>
       <c r="R13" t="n">
-        <v>6943871</v>
+        <v>6944005</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,22 +2007,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121191333</v>
+        <v>121191938</v>
       </c>
       <c r="B14" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2055,14 +2055,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493280</v>
+        <v>493264</v>
       </c>
       <c r="R14" t="n">
-        <v>6943908</v>
+        <v>6943993</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121192205</v>
+        <v>121192204</v>
       </c>
       <c r="B15" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2167,14 +2167,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493352</v>
+        <v>493338</v>
       </c>
       <c r="R15" t="n">
-        <v>6943961</v>
+        <v>6943954</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2231,22 +2231,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121192594</v>
+        <v>121191585</v>
       </c>
       <c r="B16" t="n">
-        <v>79688</v>
+        <v>78608</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,34 +2259,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tavelberget, Tavelberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493413</v>
+        <v>493220</v>
       </c>
       <c r="R16" t="n">
-        <v>6943871</v>
+        <v>6943974</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,22 +2343,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121192416</v>
+        <v>121192594</v>
       </c>
       <c r="B17" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,34 +2371,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Tavelberget, Tavelberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493333</v>
+        <v>493413</v>
       </c>
       <c r="R17" t="n">
-        <v>6943877</v>
+        <v>6943871</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2455,22 +2455,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121193050</v>
+        <v>121192421</v>
       </c>
       <c r="B18" t="n">
-        <v>57370</v>
+        <v>78608</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2483,39 +2483,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tavelberget, Tavelberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493426</v>
+        <v>493318</v>
       </c>
       <c r="R18" t="n">
-        <v>6943860</v>
+        <v>6943866</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2547,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2557,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2584,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121192891</v>
+        <v>121192356</v>
       </c>
       <c r="B19" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2620,14 +2615,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493396</v>
+        <v>493323</v>
       </c>
       <c r="R19" t="n">
-        <v>6943825</v>
+        <v>6943923</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2659,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2669,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2684,22 +2679,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121192356</v>
+        <v>121192416</v>
       </c>
       <c r="B20" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2732,14 +2727,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493323</v>
+        <v>493333</v>
       </c>
       <c r="R20" t="n">
-        <v>6943923</v>
+        <v>6943877</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2771,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2781,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2796,22 +2791,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121193685</v>
+        <v>121193050</v>
       </c>
       <c r="B21" t="n">
-        <v>78607</v>
+        <v>57371</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2824,34 +2819,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Tavelberget, Tavelberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493313</v>
+        <v>493426</v>
       </c>
       <c r="R21" t="n">
-        <v>6943851</v>
+        <v>6943860</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2908,22 +2908,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121192105</v>
+        <v>121191641</v>
       </c>
       <c r="B22" t="n">
-        <v>79688</v>
+        <v>78609</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2936,21 +2936,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>230405</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493326</v>
+        <v>493268</v>
       </c>
       <c r="R22" t="n">
-        <v>6944005</v>
+        <v>6944010</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 47122-2024 artfynd.xlsx
+++ b/artfynd/A 47122-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121193685</v>
+        <v>121191641</v>
       </c>
       <c r="B2" t="n">
-        <v>78608</v>
+        <v>78610</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493313</v>
+        <v>493268</v>
       </c>
       <c r="R2" t="n">
-        <v>6943851</v>
+        <v>6944010</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121192502</v>
+        <v>121191585</v>
       </c>
       <c r="B3" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,14 +823,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493396</v>
+        <v>493220</v>
       </c>
       <c r="R3" t="n">
-        <v>6943871</v>
+        <v>6943974</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121193372</v>
+        <v>121191337</v>
       </c>
       <c r="B4" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493418</v>
+        <v>493270</v>
       </c>
       <c r="R4" t="n">
-        <v>6943831</v>
+        <v>6943889</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121192205</v>
+        <v>121192891</v>
       </c>
       <c r="B5" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,14 +1047,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493352</v>
+        <v>493396</v>
       </c>
       <c r="R5" t="n">
-        <v>6943961</v>
+        <v>6943825</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,22 +1111,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121192891</v>
+        <v>121191329</v>
       </c>
       <c r="B6" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,14 +1159,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493396</v>
+        <v>493281</v>
       </c>
       <c r="R6" t="n">
-        <v>6943825</v>
+        <v>6943885</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,22 +1223,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121191329</v>
+        <v>121192502</v>
       </c>
       <c r="B7" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493281</v>
+        <v>493396</v>
       </c>
       <c r="R7" t="n">
-        <v>6943885</v>
+        <v>6943871</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121191415</v>
+        <v>121192105</v>
       </c>
       <c r="B8" t="n">
-        <v>78608</v>
+        <v>79690</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,34 +1363,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493234</v>
+        <v>493326</v>
       </c>
       <c r="R8" t="n">
-        <v>6943962</v>
+        <v>6944005</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,22 +1447,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121192017</v>
+        <v>121192205</v>
       </c>
       <c r="B9" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,14 +1495,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493270</v>
+        <v>493352</v>
       </c>
       <c r="R9" t="n">
-        <v>6943889</v>
+        <v>6943961</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,22 +1559,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121192106</v>
+        <v>121192594</v>
       </c>
       <c r="B10" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,14 +1607,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Tavelberget, Tavelberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493336</v>
+        <v>493413</v>
       </c>
       <c r="R10" t="n">
-        <v>6944002</v>
+        <v>6943871</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121191333</v>
+        <v>121192416</v>
       </c>
       <c r="B11" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,14 +1719,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493280</v>
+        <v>493333</v>
       </c>
       <c r="R11" t="n">
-        <v>6943908</v>
+        <v>6943877</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,22 +1783,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121192174</v>
+        <v>121193050</v>
       </c>
       <c r="B12" t="n">
-        <v>78608</v>
+        <v>57372</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,34 +1811,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Tavelberget, Tavelberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493346</v>
+        <v>493426</v>
       </c>
       <c r="R12" t="n">
-        <v>6943977</v>
+        <v>6943860</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121192105</v>
+        <v>121191938</v>
       </c>
       <c r="B13" t="n">
-        <v>79689</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,34 +1928,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493326</v>
+        <v>493264</v>
       </c>
       <c r="R13" t="n">
-        <v>6944005</v>
+        <v>6943993</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1982,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,22 +2012,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121191938</v>
+        <v>121192356</v>
       </c>
       <c r="B14" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2055,14 +2060,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bergmyren, Bergmyren, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493264</v>
+        <v>493323</v>
       </c>
       <c r="R14" t="n">
-        <v>6943993</v>
+        <v>6943923</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2094,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121192204</v>
+        <v>121192421</v>
       </c>
       <c r="B15" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2167,14 +2172,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493338</v>
+        <v>493318</v>
       </c>
       <c r="R15" t="n">
-        <v>6943954</v>
+        <v>6943866</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2206,7 +2211,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2221,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,22 +2236,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121191585</v>
+        <v>121193372</v>
       </c>
       <c r="B16" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2283,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493220</v>
+        <v>493418</v>
       </c>
       <c r="R16" t="n">
-        <v>6943974</v>
+        <v>6943831</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2318,7 +2323,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2333,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2360,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121192594</v>
+        <v>121191333</v>
       </c>
       <c r="B17" t="n">
-        <v>79689</v>
+        <v>78609</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,34 +2376,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tavelberget, Tavelberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493413</v>
+        <v>493280</v>
       </c>
       <c r="R17" t="n">
-        <v>6943871</v>
+        <v>6943908</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2430,7 +2435,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2445,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,10 +2472,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121192421</v>
+        <v>121192174</v>
       </c>
       <c r="B18" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2507,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493318</v>
+        <v>493346</v>
       </c>
       <c r="R18" t="n">
-        <v>6943866</v>
+        <v>6943977</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2542,7 +2547,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2557,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121192356</v>
+        <v>121192204</v>
       </c>
       <c r="B19" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2615,14 +2620,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
+          <t>Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493323</v>
+        <v>493338</v>
       </c>
       <c r="R19" t="n">
-        <v>6943923</v>
+        <v>6943954</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2654,7 +2659,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2669,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2679,22 +2684,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121192416</v>
+        <v>121193685</v>
       </c>
       <c r="B20" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2731,10 +2736,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493333</v>
+        <v>493313</v>
       </c>
       <c r="R20" t="n">
-        <v>6943877</v>
+        <v>6943851</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2766,7 +2771,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2781,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,10 +2808,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121193050</v>
+        <v>121192106</v>
       </c>
       <c r="B21" t="n">
-        <v>57371</v>
+        <v>79690</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2819,39 +2824,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Tavelberget, Tavelberget, Jmt</t>
+          <t>Gillerfloberget, Gillerfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493426</v>
+        <v>493336</v>
       </c>
       <c r="R21" t="n">
-        <v>6943860</v>
+        <v>6944002</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2920,7 +2920,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121191641</v>
+        <v>121191415</v>
       </c>
       <c r="B22" t="n">
         <v>78609</v>
@@ -2936,16 +2936,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2956,14 +2956,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gillerfloberget, Jmt</t>
+          <t>Bergmyren, Bergmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493268</v>
+        <v>493234</v>
       </c>
       <c r="R22" t="n">
-        <v>6944010</v>
+        <v>6943962</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3020,12 +3020,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3035,7 +3035,7 @@
         <v>121192066</v>
       </c>
       <c r="B23" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 47122-2024 artfynd.xlsx
+++ b/artfynd/A 47122-2024 artfynd.xlsx
@@ -3035,7 +3035,7 @@
         <v>121192066</v>
       </c>
       <c r="B23" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
